--- a/000_Inventario_ML_006.xlsx
+++ b/000_Inventario_ML_006.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jf.osma43\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maria Jose Vidal R\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{878DB870-1390-492D-971E-738D42796E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F070983C-53D8-4872-926D-714ACEB40871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{90BC1E0D-54BD-4111-A66F-F26C47E5F807}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{90BC1E0D-54BD-4111-A66F-F26C47E5F807}"/>
   </bookViews>
   <sheets>
     <sheet name="Listado" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="265">
   <si>
     <t>ABTS</t>
   </si>
@@ -755,6 +755,72 @@
   </si>
   <si>
     <t>Armario Nano</t>
+  </si>
+  <si>
+    <t>Gabinete de reactivos</t>
+  </si>
+  <si>
+    <t>Creative Materials lot #84701-11312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asta Tech CAT #D82039- Potassium 1,2,3,4,5,6 - Tridecafl vorohexadey sulfonate </t>
+  </si>
+  <si>
+    <t>O-phenylendiamine 987 Thermoscientific</t>
+  </si>
+  <si>
+    <t>Heptadecafluorooctanesulfonic acid potassium salt_PFOSK 987</t>
+  </si>
+  <si>
+    <t>4- Dodecylbenzene sulfonic acid</t>
+  </si>
+  <si>
+    <t>Perfluorooctanoic acid 95%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Potassium nanofluiro-1-butanesulfonate 98% </t>
+  </si>
+  <si>
+    <t>Creative materials 118-41FP lot #84730</t>
+  </si>
+  <si>
+    <t>Creative materials 102-24 lot #84698</t>
+  </si>
+  <si>
+    <t>Creative materials 102-03 lot #84700 X2</t>
+  </si>
+  <si>
+    <t>Ferrocenecarboxylic acid 97%</t>
+  </si>
+  <si>
+    <t>Perfluorooctanoic acid 97%</t>
+  </si>
+  <si>
+    <t>potassim ferrocyanide (III)</t>
+  </si>
+  <si>
+    <t>potassim ferrocyanide (II)</t>
+  </si>
+  <si>
+    <t>110g</t>
+  </si>
+  <si>
+    <t>1g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metanol </t>
+  </si>
+  <si>
+    <t>5ml</t>
+  </si>
+  <si>
+    <t>pfoa 3g</t>
+  </si>
+  <si>
+    <t>400ml</t>
+  </si>
+  <si>
+    <t>Acetate buffer pH5.8</t>
   </si>
 </sst>
 </file>
@@ -792,7 +858,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -829,6 +895,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -857,7 +929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -877,6 +949,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -889,9 +969,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -901,6 +980,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF99CC"/>
+      <color rgb="FFFF66CC"/>
       <color rgb="FF99FFCC"/>
       <color rgb="FFCC99FF"/>
       <color rgb="FFCCFF99"/>
@@ -985,7 +1066,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1281,41 +1362,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0C62C2-D98E-40F0-B246-B43ACFDAFBD0}">
-  <dimension ref="A1:C197"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D213"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.109375" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="15"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-    </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="A4" s="15"/>
-      <c r="B4" s="16" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+    </row>
+    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="C4" s="15"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C4" s="11"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>237</v>
       </c>
@@ -1326,8 +1407,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>236</v>
       </c>
       <c r="B7" s="5" t="s">
@@ -1335,281 +1416,281 @@
       </c>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="15"/>
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="15"/>
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="15"/>
       <c r="B11" s="5" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="5"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
       <c r="B12" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="5"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="15"/>
       <c r="B13" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="5"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="15"/>
       <c r="B14" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="5"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="15"/>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="5"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
       <c r="B16" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="5"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="15"/>
       <c r="B17" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="5"/>
     </row>
-    <row r="18" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
+    <row r="18" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
       <c r="B18" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C18" s="5"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="15"/>
       <c r="B19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="5"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="15"/>
       <c r="B20" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C20" s="5"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="15"/>
       <c r="B21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="5"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="15"/>
       <c r="B22" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="5"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
       <c r="B23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="5"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="15"/>
       <c r="B24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="5"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="15"/>
       <c r="B25" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="5"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="15"/>
       <c r="B26" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="5"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="15"/>
       <c r="B27" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C27" s="5"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="15"/>
       <c r="B28" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C28" s="5"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="15"/>
       <c r="B29" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C29" s="5"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="15"/>
       <c r="B30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="5"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="15"/>
       <c r="B31" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="5"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="15"/>
       <c r="B32" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C32" s="5"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="15"/>
       <c r="B33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C33" s="5"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="15"/>
       <c r="B34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="5"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="15"/>
       <c r="B35" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C35" s="5"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="15"/>
       <c r="B36" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="5"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="15"/>
       <c r="B37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C37" s="5"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="15"/>
       <c r="B38" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C38" s="5"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
+    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="15"/>
       <c r="B39" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C39" s="5"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="15"/>
       <c r="B40" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C40" s="5"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="15"/>
       <c r="B41" s="6" t="s">
         <v>32</v>
       </c>
       <c r="C41" s="5"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="15"/>
       <c r="B42" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C42" s="5"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="15"/>
       <c r="B43" s="6" t="s">
         <v>34</v>
       </c>
       <c r="C43" s="5"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="15"/>
       <c r="B44" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C44" s="5"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="15"/>
       <c r="B45" s="6" t="s">
         <v>36</v>
       </c>
       <c r="C45" s="5"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="15"/>
       <c r="B46" s="6" t="s">
         <v>37</v>
       </c>
       <c r="C46" s="5"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
         <v>240</v>
       </c>
       <c r="B47" s="7" t="s">
@@ -1619,8 +1700,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
       <c r="B48" s="7" t="s">
         <v>46</v>
       </c>
@@ -1628,8 +1709,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
       <c r="B49" s="7" t="s">
         <v>48</v>
       </c>
@@ -1637,8 +1718,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="16"/>
       <c r="B50" s="7" t="s">
         <v>50</v>
       </c>
@@ -1646,8 +1727,8 @@
         <v>54</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="16"/>
       <c r="B51" s="7" t="s">
         <v>52</v>
       </c>
@@ -1655,8 +1736,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="16"/>
       <c r="B52" s="7" t="s">
         <v>55</v>
       </c>
@@ -1664,8 +1745,8 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="16"/>
       <c r="B53" s="7" t="s">
         <v>58</v>
       </c>
@@ -1673,8 +1754,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="12"/>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="16"/>
       <c r="B54" s="7" t="s">
         <v>55</v>
       </c>
@@ -1682,8 +1763,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="16"/>
       <c r="B55" s="7" t="s">
         <v>62</v>
       </c>
@@ -1691,8 +1772,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="16"/>
       <c r="B56" s="7" t="s">
         <v>42</v>
       </c>
@@ -1700,8 +1781,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="16"/>
       <c r="B57" s="7" t="s">
         <v>67</v>
       </c>
@@ -1709,8 +1790,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="16"/>
       <c r="B58" s="7" t="s">
         <v>72</v>
       </c>
@@ -1718,8 +1799,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="16"/>
       <c r="B59" s="7" t="s">
         <v>69</v>
       </c>
@@ -1727,8 +1808,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="16"/>
       <c r="B60" s="7" t="s">
         <v>43</v>
       </c>
@@ -1736,8 +1817,8 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="16"/>
       <c r="B61" s="7" t="s">
         <v>55</v>
       </c>
@@ -1745,8 +1826,8 @@
         <v>73</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="16"/>
       <c r="B62" s="7" t="s">
         <v>69</v>
       </c>
@@ -1754,8 +1835,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="16"/>
       <c r="B63" s="7" t="s">
         <v>75</v>
       </c>
@@ -1763,8 +1844,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="16"/>
       <c r="B64" s="7" t="s">
         <v>76</v>
       </c>
@@ -1772,8 +1853,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="16"/>
       <c r="B65" s="7" t="s">
         <v>81</v>
       </c>
@@ -1781,8 +1862,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="16"/>
       <c r="B66" s="7" t="s">
         <v>82</v>
       </c>
@@ -1790,8 +1871,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="16"/>
       <c r="B67" s="7" t="s">
         <v>83</v>
       </c>
@@ -1799,8 +1880,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="16"/>
       <c r="B68" s="7" t="s">
         <v>85</v>
       </c>
@@ -1808,8 +1889,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="12"/>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="16"/>
       <c r="B69" s="7" t="s">
         <v>86</v>
       </c>
@@ -1817,8 +1898,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="12"/>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="16"/>
       <c r="B70" s="7" t="s">
         <v>87</v>
       </c>
@@ -1826,8 +1907,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="16"/>
       <c r="B71" s="7" t="s">
         <v>42</v>
       </c>
@@ -1835,8 +1916,8 @@
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="12"/>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="16"/>
       <c r="B72" s="7" t="s">
         <v>113</v>
       </c>
@@ -1844,8 +1925,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="16"/>
       <c r="B73" s="7" t="s">
         <v>42</v>
       </c>
@@ -1853,8 +1934,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="12"/>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="16"/>
       <c r="B74" s="7" t="s">
         <v>141</v>
       </c>
@@ -1862,8 +1943,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="12"/>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="16"/>
       <c r="B75" s="7" t="s">
         <v>158</v>
       </c>
@@ -1871,8 +1952,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="12"/>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="16"/>
       <c r="B76" s="7" t="s">
         <v>159</v>
       </c>
@@ -1880,8 +1961,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="12"/>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="16"/>
       <c r="B77" s="7" t="s">
         <v>161</v>
       </c>
@@ -1889,8 +1970,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="12"/>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="16"/>
       <c r="B78" s="7" t="s">
         <v>162</v>
       </c>
@@ -1898,15 +1979,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="12"/>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="16"/>
       <c r="B79" s="7" t="s">
         <v>198</v>
       </c>
       <c r="C79" s="7"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="13" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
         <v>241</v>
       </c>
       <c r="B80" s="8" t="s">
@@ -1916,8 +1997,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="13"/>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="17"/>
       <c r="B81" s="8" t="s">
         <v>89</v>
       </c>
@@ -1925,8 +2006,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="13"/>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="17"/>
       <c r="B82" s="8" t="s">
         <v>90</v>
       </c>
@@ -1934,8 +2015,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="13"/>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="17"/>
       <c r="B83" s="8" t="s">
         <v>92</v>
       </c>
@@ -1943,8 +2024,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="13"/>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="17"/>
       <c r="B84" s="8" t="s">
         <v>93</v>
       </c>
@@ -1952,8 +2033,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="13"/>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="17"/>
       <c r="B85" s="8" t="s">
         <v>94</v>
       </c>
@@ -1961,8 +2042,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="13"/>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="17"/>
       <c r="B86" s="8" t="s">
         <v>95</v>
       </c>
@@ -1970,8 +2051,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="13"/>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="17"/>
       <c r="B87" s="8" t="s">
         <v>96</v>
       </c>
@@ -1979,8 +2060,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="13"/>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="17"/>
       <c r="B88" s="8" t="s">
         <v>97</v>
       </c>
@@ -1988,8 +2069,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="13"/>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="17"/>
       <c r="B89" s="8" t="s">
         <v>99</v>
       </c>
@@ -1997,8 +2078,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="13"/>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="17"/>
       <c r="B90" s="8" t="s">
         <v>100</v>
       </c>
@@ -2006,8 +2087,8 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="13"/>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="17"/>
       <c r="B91" s="8" t="s">
         <v>101</v>
       </c>
@@ -2015,8 +2096,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="13"/>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="17"/>
       <c r="B92" s="8" t="s">
         <v>102</v>
       </c>
@@ -2024,8 +2105,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="13"/>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="17"/>
       <c r="B93" s="8" t="s">
         <v>103</v>
       </c>
@@ -2033,8 +2114,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="13"/>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="17"/>
       <c r="B94" s="8" t="s">
         <v>90</v>
       </c>
@@ -2042,8 +2123,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="13"/>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="17"/>
       <c r="B95" s="8" t="s">
         <v>104</v>
       </c>
@@ -2051,8 +2132,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="13"/>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="17"/>
       <c r="B96" s="8" t="s">
         <v>100</v>
       </c>
@@ -2060,8 +2141,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="13"/>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="17"/>
       <c r="B97" s="8" t="s">
         <v>106</v>
       </c>
@@ -2069,8 +2150,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="13"/>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="17"/>
       <c r="B98" s="8" t="s">
         <v>107</v>
       </c>
@@ -2078,8 +2159,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="13"/>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="17"/>
       <c r="B99" s="8" t="s">
         <v>109</v>
       </c>
@@ -2087,15 +2168,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="13"/>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="17"/>
       <c r="B100" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C100" s="8"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="13"/>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="17"/>
       <c r="B101" s="8" t="s">
         <v>112</v>
       </c>
@@ -2103,8 +2184,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="13"/>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="17"/>
       <c r="B102" s="8" t="s">
         <v>114</v>
       </c>
@@ -2112,8 +2193,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="13"/>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="17"/>
       <c r="B103" s="8" t="s">
         <v>116</v>
       </c>
@@ -2121,8 +2202,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A104" s="13"/>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="17"/>
       <c r="B104" s="8" t="s">
         <v>117</v>
       </c>
@@ -2130,8 +2211,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A105" s="13"/>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="17"/>
       <c r="B105" s="8" t="s">
         <v>118</v>
       </c>
@@ -2139,8 +2220,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A106" s="13"/>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="17"/>
       <c r="B106" s="8" t="s">
         <v>120</v>
       </c>
@@ -2148,8 +2229,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A107" s="13"/>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="17"/>
       <c r="B107" s="8" t="s">
         <v>134</v>
       </c>
@@ -2157,8 +2238,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A108" s="13"/>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="17"/>
       <c r="B108" s="8" t="s">
         <v>116</v>
       </c>
@@ -2166,8 +2247,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A109" s="13"/>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="17"/>
       <c r="B109" s="8" t="s">
         <v>155</v>
       </c>
@@ -2175,8 +2256,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A110" s="13"/>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="17"/>
       <c r="B110" s="8" t="s">
         <v>156</v>
       </c>
@@ -2184,8 +2265,8 @@
         <v>157</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A111" s="13"/>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="17"/>
       <c r="B111" s="8" t="s">
         <v>169</v>
       </c>
@@ -2193,8 +2274,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A112" s="13"/>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="17"/>
       <c r="B112" s="8" t="s">
         <v>179</v>
       </c>
@@ -2202,8 +2283,8 @@
         <v>190</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A113" s="13"/>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="17"/>
       <c r="B113" s="8" t="s">
         <v>189</v>
       </c>
@@ -2211,8 +2292,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A114" s="13"/>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="17"/>
       <c r="B114" s="8" t="s">
         <v>191</v>
       </c>
@@ -2220,8 +2301,8 @@
         <v>192</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A115" s="13"/>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="17"/>
       <c r="B115" s="8" t="s">
         <v>193</v>
       </c>
@@ -2229,15 +2310,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A116" s="13"/>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="17"/>
       <c r="B116" s="8" t="s">
         <v>78</v>
       </c>
       <c r="C116" s="8"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A117" s="13"/>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="17"/>
       <c r="B117" s="8" t="s">
         <v>79</v>
       </c>
@@ -2245,8 +2326,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A118" s="13"/>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="17"/>
       <c r="B118" s="8" t="s">
         <v>111</v>
       </c>
@@ -2254,8 +2335,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A119" s="13"/>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="17"/>
       <c r="B119" s="8" t="s">
         <v>121</v>
       </c>
@@ -2263,8 +2344,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A120" s="13"/>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="17"/>
       <c r="B120" s="8" t="s">
         <v>122</v>
       </c>
@@ -2272,8 +2353,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A121" s="13"/>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="17"/>
       <c r="B121" s="8" t="s">
         <v>123</v>
       </c>
@@ -2281,8 +2362,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A122" s="13"/>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="17"/>
       <c r="B122" s="8" t="s">
         <v>124</v>
       </c>
@@ -2290,8 +2371,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A123" s="13"/>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="17"/>
       <c r="B123" s="8" t="s">
         <v>125</v>
       </c>
@@ -2299,8 +2380,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A124" s="13"/>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="17"/>
       <c r="B124" s="8" t="s">
         <v>126</v>
       </c>
@@ -2308,8 +2389,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A125" s="13"/>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="17"/>
       <c r="B125" s="8" t="s">
         <v>128</v>
       </c>
@@ -2317,8 +2398,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A126" s="13"/>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="17"/>
       <c r="B126" s="8" t="s">
         <v>130</v>
       </c>
@@ -2326,8 +2407,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A127" s="13"/>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="17"/>
       <c r="B127" s="8" t="s">
         <v>129</v>
       </c>
@@ -2335,8 +2416,8 @@
         <v>70</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A128" s="13"/>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="17"/>
       <c r="B128" s="8" t="s">
         <v>131</v>
       </c>
@@ -2344,8 +2425,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A129" s="13"/>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="17"/>
       <c r="B129" s="8" t="s">
         <v>133</v>
       </c>
@@ -2353,8 +2434,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A130" s="13"/>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="17"/>
       <c r="B130" s="8" t="s">
         <v>123</v>
       </c>
@@ -2362,8 +2443,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A131" s="13"/>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="17"/>
       <c r="B131" s="8" t="s">
         <v>176</v>
       </c>
@@ -2371,8 +2452,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A132" s="13"/>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="17"/>
       <c r="B132" s="8" t="s">
         <v>136</v>
       </c>
@@ -2380,8 +2461,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A133" s="13"/>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="17"/>
       <c r="B133" s="8" t="s">
         <v>137</v>
       </c>
@@ -2389,8 +2470,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A134" s="13"/>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="17"/>
       <c r="B134" s="8" t="s">
         <v>139</v>
       </c>
@@ -2398,8 +2479,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A135" s="13"/>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="17"/>
       <c r="B135" s="8" t="s">
         <v>140</v>
       </c>
@@ -2407,8 +2488,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A136" s="13"/>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="17"/>
       <c r="B136" s="8" t="s">
         <v>142</v>
       </c>
@@ -2416,8 +2497,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A137" s="13"/>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="17"/>
       <c r="B137" s="8" t="s">
         <v>143</v>
       </c>
@@ -2425,8 +2506,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A138" s="13"/>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="17"/>
       <c r="B138" s="8" t="s">
         <v>130</v>
       </c>
@@ -2434,8 +2515,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A139" s="13"/>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="17"/>
       <c r="B139" s="8" t="s">
         <v>144</v>
       </c>
@@ -2443,8 +2524,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A140" s="13"/>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="17"/>
       <c r="B140" s="8" t="s">
         <v>145</v>
       </c>
@@ -2452,8 +2533,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A141" s="13"/>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="17"/>
       <c r="B141" s="8" t="s">
         <v>146</v>
       </c>
@@ -2461,8 +2542,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A142" s="13"/>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="17"/>
       <c r="B142" s="8" t="s">
         <v>147</v>
       </c>
@@ -2470,8 +2551,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A143" s="13"/>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="17"/>
       <c r="B143" s="8" t="s">
         <v>149</v>
       </c>
@@ -2479,8 +2560,8 @@
         <v>150</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A144" s="13"/>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="17"/>
       <c r="B144" s="8" t="s">
         <v>151</v>
       </c>
@@ -2488,8 +2569,8 @@
         <v>71</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A145" s="13"/>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="17"/>
       <c r="B145" s="8" t="s">
         <v>144</v>
       </c>
@@ -2497,8 +2578,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A146" s="13"/>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="17"/>
       <c r="B146" s="8" t="s">
         <v>153</v>
       </c>
@@ -2506,8 +2587,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A147" s="13"/>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="17"/>
       <c r="B147" s="8" t="s">
         <v>153</v>
       </c>
@@ -2515,8 +2596,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A148" s="13"/>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="17"/>
       <c r="B148" s="8" t="s">
         <v>154</v>
       </c>
@@ -2524,8 +2605,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A149" s="13"/>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="17"/>
       <c r="B149" s="8" t="s">
         <v>153</v>
       </c>
@@ -2533,8 +2614,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A150" s="13"/>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="17"/>
       <c r="B150" s="8" t="s">
         <v>153</v>
       </c>
@@ -2542,8 +2623,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A151" s="13"/>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="17"/>
       <c r="B151" s="8" t="s">
         <v>164</v>
       </c>
@@ -2551,8 +2632,8 @@
         <v>132</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A152" s="13"/>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="17"/>
       <c r="B152" s="8" t="s">
         <v>165</v>
       </c>
@@ -2560,8 +2641,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A153" s="13"/>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="17"/>
       <c r="B153" s="8" t="s">
         <v>166</v>
       </c>
@@ -2569,8 +2650,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A154" s="13"/>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="17"/>
       <c r="B154" s="8" t="s">
         <v>167</v>
       </c>
@@ -2578,8 +2659,8 @@
         <v>168</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A155" s="13"/>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="17"/>
       <c r="B155" s="8" t="s">
         <v>171</v>
       </c>
@@ -2587,8 +2668,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A156" s="13"/>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="17"/>
       <c r="B156" s="8" t="s">
         <v>173</v>
       </c>
@@ -2596,8 +2677,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A157" s="13"/>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="17"/>
       <c r="B157" s="8" t="s">
         <v>174</v>
       </c>
@@ -2605,8 +2686,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A158" s="13"/>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="17"/>
       <c r="B158" s="8" t="s">
         <v>175</v>
       </c>
@@ -2614,8 +2695,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A159" s="13"/>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="17"/>
       <c r="B159" s="8" t="s">
         <v>177</v>
       </c>
@@ -2623,8 +2704,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A160" s="13"/>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="17"/>
       <c r="B160" s="8" t="s">
         <v>178</v>
       </c>
@@ -2632,8 +2713,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A161" s="13"/>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="17"/>
       <c r="B161" s="8" t="s">
         <v>181</v>
       </c>
@@ -2641,8 +2722,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A162" s="13"/>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="17"/>
       <c r="B162" s="8" t="s">
         <v>182</v>
       </c>
@@ -2650,8 +2731,8 @@
         <v>183</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A163" s="13"/>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="17"/>
       <c r="B163" s="8" t="s">
         <v>184</v>
       </c>
@@ -2659,8 +2740,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A164" s="13"/>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="17"/>
       <c r="B164" s="8" t="s">
         <v>185</v>
       </c>
@@ -2668,8 +2749,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A165" s="13"/>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="17"/>
       <c r="B165" s="8" t="s">
         <v>186</v>
       </c>
@@ -2677,8 +2758,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A166" s="13"/>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="17"/>
       <c r="B166" s="8" t="s">
         <v>187</v>
       </c>
@@ -2686,8 +2767,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A167" s="13"/>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="17"/>
       <c r="B167" s="8" t="s">
         <v>188</v>
       </c>
@@ -2695,8 +2776,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A168" s="13"/>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="17"/>
       <c r="B168" s="8" t="s">
         <v>199</v>
       </c>
@@ -2704,15 +2785,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A169" s="13"/>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="17"/>
       <c r="B169" s="8" t="s">
         <v>194</v>
       </c>
       <c r="C169" s="8"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A170" s="13"/>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="17"/>
       <c r="B170" s="8" t="s">
         <v>195</v>
       </c>
@@ -2720,8 +2801,8 @@
         <v>196</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A171" s="13"/>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="17"/>
       <c r="B171" s="8" t="s">
         <v>197</v>
       </c>
@@ -2729,8 +2810,8 @@
         <v>200</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A172" s="13"/>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="17"/>
       <c r="B172" s="8" t="s">
         <v>201</v>
       </c>
@@ -2738,8 +2819,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A173" s="13"/>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="17"/>
       <c r="B173" s="8" t="s">
         <v>202</v>
       </c>
@@ -2747,8 +2828,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A174" s="14" t="s">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="18" t="s">
         <v>242</v>
       </c>
       <c r="B174" s="9" t="s">
@@ -2758,8 +2839,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A175" s="14"/>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="18"/>
       <c r="B175" s="9" t="s">
         <v>203</v>
       </c>
@@ -2767,8 +2848,8 @@
         <v>135</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A176" s="14"/>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="18"/>
       <c r="B176" s="9" t="s">
         <v>203</v>
       </c>
@@ -2776,8 +2857,8 @@
         <v>204</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A177" s="14"/>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="18"/>
       <c r="B177" s="9" t="s">
         <v>205</v>
       </c>
@@ -2785,8 +2866,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A178" s="14"/>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="18"/>
       <c r="B178" s="9" t="s">
         <v>206</v>
       </c>
@@ -2794,8 +2875,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A179" s="14"/>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="18"/>
       <c r="B179" s="9" t="s">
         <v>207</v>
       </c>
@@ -2803,8 +2884,8 @@
         <v>51</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A180" s="14"/>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="18"/>
       <c r="B180" s="9" t="s">
         <v>209</v>
       </c>
@@ -2812,8 +2893,8 @@
         <v>170</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A181" s="14"/>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="18"/>
       <c r="B181" s="9" t="s">
         <v>210</v>
       </c>
@@ -2821,8 +2902,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A182" s="14"/>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="18"/>
       <c r="B182" s="9" t="s">
         <v>222</v>
       </c>
@@ -2830,8 +2911,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A183" s="14"/>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="18"/>
       <c r="B183" s="9" t="s">
         <v>211</v>
       </c>
@@ -2839,8 +2920,8 @@
         <v>212</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A184" s="14"/>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="18"/>
       <c r="B184" s="9" t="s">
         <v>213</v>
       </c>
@@ -2848,8 +2929,8 @@
         <v>214</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A185" s="14"/>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="18"/>
       <c r="B185" s="9" t="s">
         <v>215</v>
       </c>
@@ -2857,8 +2938,8 @@
         <v>216</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A186" s="14"/>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="18"/>
       <c r="B186" s="9" t="s">
         <v>219</v>
       </c>
@@ -2866,8 +2947,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A187" s="14"/>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="18"/>
       <c r="B187" s="9" t="s">
         <v>217</v>
       </c>
@@ -2875,8 +2956,8 @@
         <v>220</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A188" s="14"/>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="18"/>
       <c r="B188" s="9" t="s">
         <v>218</v>
       </c>
@@ -2884,8 +2965,8 @@
         <v>221</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A189" s="14"/>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="18"/>
       <c r="B189" s="9" t="s">
         <v>223</v>
       </c>
@@ -2893,8 +2974,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A190" s="14"/>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="18"/>
       <c r="B190" s="9" t="s">
         <v>224</v>
       </c>
@@ -2902,8 +2983,8 @@
         <v>60</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A191" s="14"/>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="18"/>
       <c r="B191" s="9" t="s">
         <v>225</v>
       </c>
@@ -2911,8 +2992,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A192" s="14"/>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="18"/>
       <c r="B192" s="9" t="s">
         <v>228</v>
       </c>
@@ -2920,8 +3001,8 @@
         <v>61</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A193" s="14"/>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A193" s="18"/>
       <c r="B193" s="9" t="s">
         <v>217</v>
       </c>
@@ -2929,8 +3010,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A194" s="14"/>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A194" s="18"/>
       <c r="B194" s="9" t="s">
         <v>225</v>
       </c>
@@ -2938,8 +3019,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A195" s="14"/>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A195" s="18"/>
       <c r="B195" s="9" t="s">
         <v>231</v>
       </c>
@@ -2947,8 +3028,8 @@
         <v>232</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" s="14"/>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A196" s="18"/>
       <c r="B196" s="9" t="s">
         <v>233</v>
       </c>
@@ -2956,8 +3037,8 @@
         <v>63</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" s="14"/>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A197" s="18"/>
       <c r="B197" s="9" t="s">
         <v>234</v>
       </c>
@@ -2965,12 +3046,162 @@
         <v>235</v>
       </c>
     </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A198" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B198" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="C198" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A199" s="19"/>
+      <c r="B199" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C199" s="13" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A200" s="19"/>
+      <c r="B200" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C200" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A201" s="19"/>
+      <c r="B201" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C201" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="19"/>
+      <c r="B202" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="C202" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="19"/>
+      <c r="B203" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C203" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A204" s="19"/>
+      <c r="B204" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="C204" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D204" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A205" s="19"/>
+      <c r="B205" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C205" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A206" s="19"/>
+      <c r="B206" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C206" s="13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A207" s="19"/>
+      <c r="B207" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C207" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A208" s="19"/>
+      <c r="B208" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C208" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="19"/>
+      <c r="B209" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="C209" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="19"/>
+      <c r="B210" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="C210" s="13" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="19"/>
+      <c r="B211" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C211" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="19"/>
+      <c r="B212" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="C212" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="19"/>
+      <c r="B213" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="C213" s="13" t="s">
+        <v>261</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A7:A46"/>
     <mergeCell ref="A47:A79"/>
     <mergeCell ref="A80:A173"/>
     <mergeCell ref="A174:A197"/>
+    <mergeCell ref="A198:A213"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2980,16 +3211,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{296316FE-8489-4B2D-9C3B-FCD889658DC0}">
   <dimension ref="A1:F159"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="54.44140625" customWidth="1"/>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="54.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -2997,7 +3228,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3015,7 +3246,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3033,7 +3264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3051,7 +3282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -3069,7 +3300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -3087,7 +3318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -3105,7 +3336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3123,7 +3354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -3140,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -3158,7 +3389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -3172,7 +3403,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -3187,7 +3418,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>3</v>
       </c>
@@ -3201,7 +3432,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -3216,7 +3447,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>4</v>
       </c>
@@ -3230,7 +3461,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -3245,7 +3476,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
@@ -3259,7 +3490,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -3277,7 +3508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -3292,7 +3523,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -3303,7 +3534,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>7</v>
       </c>
@@ -3314,7 +3545,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>19</v>
       </c>
@@ -3325,7 +3556,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
@@ -3336,7 +3567,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>21</v>
       </c>
@@ -3347,7 +3578,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>23</v>
       </c>
@@ -3358,7 +3589,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>0</v>
       </c>
@@ -3369,7 +3600,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>24</v>
       </c>
@@ -3380,7 +3611,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>25</v>
       </c>
@@ -3394,7 +3625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>26</v>
       </c>
@@ -3405,7 +3636,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>26</v>
       </c>
@@ -3416,7 +3647,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>27</v>
       </c>
@@ -3427,7 +3658,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>28</v>
       </c>
@@ -3438,7 +3669,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>29</v>
       </c>
@@ -3449,7 +3680,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>30</v>
       </c>
@@ -3460,27 +3691,27 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>35</v>
       </c>
@@ -3488,7 +3719,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>36</v>
       </c>
@@ -3505,7 +3736,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>37</v>
       </c>
@@ -3519,7 +3750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
         <v>90</v>
       </c>
@@ -3527,7 +3758,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
         <v>92</v>
       </c>
@@ -3538,7 +3769,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
         <v>93</v>
       </c>
@@ -3546,7 +3777,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
         <v>94</v>
       </c>
@@ -3554,7 +3785,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C46" t="s">
         <v>95</v>
       </c>
@@ -3562,7 +3793,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C47" t="s">
         <v>96</v>
       </c>
@@ -3570,7 +3801,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C48" t="s">
         <v>97</v>
       </c>
@@ -3578,7 +3809,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="49" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C49" t="s">
         <v>99</v>
       </c>
@@ -3586,7 +3817,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C50" t="s">
         <v>100</v>
       </c>
@@ -3597,7 +3828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C51" t="s">
         <v>101</v>
       </c>
@@ -3608,7 +3839,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C52" t="s">
         <v>102</v>
       </c>
@@ -3616,7 +3847,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C53" t="s">
         <v>103</v>
       </c>
@@ -3627,7 +3858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C54" t="s">
         <v>90</v>
       </c>
@@ -3635,7 +3866,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C55" t="s">
         <v>104</v>
       </c>
@@ -3643,7 +3874,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
         <v>100</v>
       </c>
@@ -3651,7 +3882,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C57" t="s">
         <v>106</v>
       </c>
@@ -3662,7 +3893,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C58" t="s">
         <v>107</v>
       </c>
@@ -3670,7 +3901,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="59" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C59" t="s">
         <v>109</v>
       </c>
@@ -3678,12 +3909,12 @@
         <v>108</v>
       </c>
     </row>
-    <row r="60" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C60" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="61" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C61" t="s">
         <v>112</v>
       </c>
@@ -3691,7 +3922,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="62" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C62" t="s">
         <v>114</v>
       </c>
@@ -3699,7 +3930,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="63" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C63" t="s">
         <v>116</v>
       </c>
@@ -3710,7 +3941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C64" t="s">
         <v>117</v>
       </c>
@@ -3718,7 +3949,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C65" t="s">
         <v>118</v>
       </c>
@@ -3726,7 +3957,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C66" t="s">
         <v>120</v>
       </c>
@@ -3734,7 +3965,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="67" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C67" t="s">
         <v>134</v>
       </c>
@@ -3742,7 +3973,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C68" t="s">
         <v>116</v>
       </c>
@@ -3750,7 +3981,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C69" t="s">
         <v>155</v>
       </c>
@@ -3758,7 +3989,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="70" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C70" t="s">
         <v>156</v>
       </c>
@@ -3766,7 +3997,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="71" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C71" t="s">
         <v>169</v>
       </c>
@@ -3774,7 +4005,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="72" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C72" t="s">
         <v>179</v>
       </c>
@@ -3782,7 +4013,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="73" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C73" t="s">
         <v>189</v>
       </c>
@@ -3790,7 +4021,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="74" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C74" t="s">
         <v>191</v>
       </c>
@@ -3798,7 +4029,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="75" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C75" t="s">
         <v>193</v>
       </c>
@@ -3806,12 +4037,12 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C76" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="77" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C77" t="s">
         <v>79</v>
       </c>
@@ -3825,7 +4056,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="78" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C78" t="s">
         <v>111</v>
       </c>
@@ -3836,7 +4067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C79" t="s">
         <v>121</v>
       </c>
@@ -3844,7 +4075,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C80" t="s">
         <v>122</v>
       </c>
@@ -3852,7 +4083,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C81" t="s">
         <v>123</v>
       </c>
@@ -3860,7 +4091,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C82" t="s">
         <v>124</v>
       </c>
@@ -3868,7 +4099,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="83" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C83" t="s">
         <v>125</v>
       </c>
@@ -3876,7 +4107,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="84" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C84" t="s">
         <v>126</v>
       </c>
@@ -3884,7 +4115,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="85" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C85" t="s">
         <v>128</v>
       </c>
@@ -3895,7 +4126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C86" t="s">
         <v>130</v>
       </c>
@@ -3903,7 +4134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="87" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C87" t="s">
         <v>129</v>
       </c>
@@ -3911,7 +4142,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="88" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C88" t="s">
         <v>131</v>
       </c>
@@ -3919,7 +4150,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="89" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C89" t="s">
         <v>133</v>
       </c>
@@ -3927,7 +4158,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="90" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C90" t="s">
         <v>123</v>
       </c>
@@ -3938,7 +4169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C91" t="s">
         <v>176</v>
       </c>
@@ -3949,7 +4180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C92" t="s">
         <v>136</v>
       </c>
@@ -3957,7 +4188,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="93" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C93" t="s">
         <v>137</v>
       </c>
@@ -3965,7 +4196,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="94" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C94" t="s">
         <v>139</v>
       </c>
@@ -3973,7 +4204,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="95" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C95" t="s">
         <v>140</v>
       </c>
@@ -3981,7 +4212,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C96" t="s">
         <v>142</v>
       </c>
@@ -3989,7 +4220,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="97" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C97" t="s">
         <v>143</v>
       </c>
@@ -3997,7 +4228,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="98" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C98" t="s">
         <v>130</v>
       </c>
@@ -4005,7 +4236,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="99" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C99" t="s">
         <v>144</v>
       </c>
@@ -4016,7 +4247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C100" t="s">
         <v>145</v>
       </c>
@@ -4024,7 +4255,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="101" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C101" t="s">
         <v>146</v>
       </c>
@@ -4032,7 +4263,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="102" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C102" t="s">
         <v>147</v>
       </c>
@@ -4040,7 +4271,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="103" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C103" t="s">
         <v>149</v>
       </c>
@@ -4048,7 +4279,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="104" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C104" t="s">
         <v>151</v>
       </c>
@@ -4056,7 +4287,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="105" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C105" t="s">
         <v>144</v>
       </c>
@@ -4064,7 +4295,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="106" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C106" t="s">
         <v>153</v>
       </c>
@@ -4075,7 +4306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C107" t="s">
         <v>153</v>
       </c>
@@ -4086,7 +4317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C108" t="s">
         <v>154</v>
       </c>
@@ -4094,7 +4325,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="109" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C109" t="s">
         <v>153</v>
       </c>
@@ -4105,7 +4336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C110" t="s">
         <v>153</v>
       </c>
@@ -4113,7 +4344,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="111" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C111" t="s">
         <v>164</v>
       </c>
@@ -4121,7 +4352,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="112" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C112" t="s">
         <v>165</v>
       </c>
@@ -4129,7 +4360,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C113" t="s">
         <v>166</v>
       </c>
@@ -4137,7 +4368,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="114" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C114" t="s">
         <v>167</v>
       </c>
@@ -4145,7 +4376,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="115" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C115" t="s">
         <v>171</v>
       </c>
@@ -4153,7 +4384,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="116" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C116" t="s">
         <v>173</v>
       </c>
@@ -4161,7 +4392,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C117" t="s">
         <v>174</v>
       </c>
@@ -4169,7 +4400,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="118" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C118" t="s">
         <v>175</v>
       </c>
@@ -4177,7 +4408,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="119" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C119" t="s">
         <v>177</v>
       </c>
@@ -4185,7 +4416,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="120" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C120" t="s">
         <v>178</v>
       </c>
@@ -4193,7 +4424,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="121" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C121" t="s">
         <v>181</v>
       </c>
@@ -4201,7 +4432,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="122" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C122" t="s">
         <v>182</v>
       </c>
@@ -4209,7 +4440,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="123" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C123" t="s">
         <v>184</v>
       </c>
@@ -4217,7 +4448,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="124" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C124" t="s">
         <v>185</v>
       </c>
@@ -4225,7 +4456,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="125" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C125" t="s">
         <v>186</v>
       </c>
@@ -4233,7 +4464,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="126" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C126" t="s">
         <v>187</v>
       </c>
@@ -4241,7 +4472,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="127" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C127" t="s">
         <v>188</v>
       </c>
@@ -4252,7 +4483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C128" t="s">
         <v>199</v>
       </c>
@@ -4263,12 +4494,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C129" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="130" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C130" t="s">
         <v>195</v>
       </c>
@@ -4279,7 +4510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C131" t="s">
         <v>197</v>
       </c>
@@ -4290,7 +4521,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="132" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C132" t="s">
         <v>201</v>
       </c>
@@ -4301,7 +4532,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="133" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C133" t="s">
         <v>202</v>
       </c>
@@ -4312,12 +4543,12 @@
         <v>61</v>
       </c>
     </row>
-    <row r="135" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C135" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="136" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C136" t="s">
         <v>208</v>
       </c>
@@ -4325,7 +4556,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="137" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C137" t="s">
         <v>203</v>
       </c>
@@ -4333,7 +4564,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C138" t="s">
         <v>203</v>
       </c>
@@ -4341,7 +4572,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="139" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C139" t="s">
         <v>205</v>
       </c>
@@ -4349,7 +4580,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="140" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C140" t="s">
         <v>206</v>
       </c>
@@ -4357,7 +4588,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="141" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C141" t="s">
         <v>207</v>
       </c>
@@ -4365,7 +4596,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="142" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C142" t="s">
         <v>209</v>
       </c>
@@ -4376,7 +4607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C143" t="s">
         <v>210</v>
       </c>
@@ -4384,7 +4615,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="144" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C144" t="s">
         <v>222</v>
       </c>
@@ -4392,7 +4623,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="145" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="145" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C145" t="s">
         <v>211</v>
       </c>
@@ -4400,7 +4631,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="146" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="146" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C146" t="s">
         <v>213</v>
       </c>
@@ -4408,7 +4639,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="147" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C147" t="s">
         <v>215</v>
       </c>
@@ -4416,7 +4647,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="148" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="148" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C148" t="s">
         <v>219</v>
       </c>
@@ -4424,7 +4655,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="149" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="149" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C149" t="s">
         <v>217</v>
       </c>
@@ -4432,7 +4663,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="150" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="150" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C150" t="s">
         <v>218</v>
       </c>
@@ -4440,7 +4671,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="151" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="151" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C151" t="s">
         <v>223</v>
       </c>
@@ -4448,7 +4679,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="152" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="152" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C152" t="s">
         <v>224</v>
       </c>
@@ -4456,7 +4687,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="153" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="153" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C153" t="s">
         <v>225</v>
       </c>
@@ -4467,7 +4698,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="154" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="154" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C154" t="s">
         <v>228</v>
       </c>
@@ -4478,7 +4709,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="155" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="155" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C155" t="s">
         <v>217</v>
       </c>
@@ -4486,7 +4717,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="156" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="156" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C156" t="s">
         <v>225</v>
       </c>
@@ -4497,7 +4728,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="157" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="157" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C157" t="s">
         <v>231</v>
       </c>
@@ -4505,7 +4736,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="158" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="158" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C158" t="s">
         <v>233</v>
       </c>
@@ -4513,7 +4744,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="159" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="159" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C159" t="s">
         <v>234</v>
       </c>
